--- a/DARS TAQSIMOT.xlsx
+++ b/DARS TAQSIMOT.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="8400"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22185" windowHeight="8400"/>
   </bookViews>
   <sheets>
     <sheet name="1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="144525"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="84">
   <si>
     <t>#</t>
   </si>
@@ -98,30 +98,12 @@
     <t>6</t>
   </si>
   <si>
-    <t>Xazratqulov Muxtor8</t>
-  </si>
-  <si>
-    <t>Xazratqulov Muxtor10</t>
-  </si>
-  <si>
-    <t>Xazratqulov Muxtor11</t>
-  </si>
-  <si>
     <t>Oqilova Gullola</t>
   </si>
   <si>
     <t>Nematov Ilxomjon</t>
   </si>
   <si>
-    <t>Fayzullayev Ro'ziqul5</t>
-  </si>
-  <si>
-    <t>Fayzullayev Ro'ziqul7</t>
-  </si>
-  <si>
-    <t>Fayzullayev Ro'ziqul9</t>
-  </si>
-  <si>
     <t>Fayziyev Nodirbek</t>
   </si>
   <si>
@@ -152,24 +134,9 @@
     <t>Matematika</t>
   </si>
   <si>
-    <t>Jurayev Jamshid8</t>
-  </si>
-  <si>
-    <t>Jurayev Jamshid10</t>
-  </si>
-  <si>
-    <t>Jurayev Jamshid11</t>
-  </si>
-  <si>
     <t>Norqulov Egamberdi</t>
   </si>
   <si>
-    <t>Norqulov Egamberdi7</t>
-  </si>
-  <si>
-    <t>Norqulov Egamberdi9</t>
-  </si>
-  <si>
     <t>Mamatov Elyorjon</t>
   </si>
   <si>
@@ -309,19 +276,16 @@
   </si>
   <si>
     <t>Xoliqulov Umar</t>
+  </si>
+  <si>
+    <t>Fayzullayev Ro'ziqul</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="21">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -335,151 +299,8 @@
       <name val="Times New Roman"/>
       <charset val="204"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri Light"/>
-      <charset val="134"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C5700"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="35">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -488,7 +309,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.79995117038483843"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -498,194 +319,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="11">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -708,178 +343,9 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.399975585192419"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -910,57 +376,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Link" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
+  <cellStyles count="1">
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1222,21 +641,21 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:S114"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="4.42592592592593" style="1" customWidth="1"/>
+    <col min="1" max="1" width="4.42578125" style="1" customWidth="1"/>
     <col min="2" max="2" width="23" style="1" customWidth="1"/>
     <col min="3" max="3" width="27" style="1" customWidth="1"/>
-    <col min="4" max="4" width="5.71296296296296" style="1" customWidth="1"/>
-    <col min="5" max="19" width="4.71296296296296" style="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.13888888888889" style="1"/>
+    <col min="4" max="4" width="5.7109375" style="1" customWidth="1"/>
+    <col min="5" max="19" width="4.7109375" style="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19">
@@ -1560,7 +979,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>21</v>
@@ -1589,7 +1008,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>21</v>
@@ -1618,7 +1037,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>21</v>
@@ -1647,7 +1066,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>21</v>
@@ -1700,7 +1119,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>21</v>
@@ -1733,7 +1152,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>28</v>
+        <v>83</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>21</v>
@@ -1762,7 +1181,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>29</v>
+        <v>83</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>21</v>
@@ -1791,7 +1210,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>30</v>
+        <v>83</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>21</v>
@@ -1820,10 +1239,10 @@
         <v>15</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D15" s="5"/>
       <c r="E15" s="6" t="s">
@@ -1873,10 +1292,10 @@
         <v>16</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D16" s="5"/>
       <c r="E16" s="6"/>
@@ -1891,16 +1310,16 @@
       <c r="N16" s="7"/>
       <c r="O16" s="7"/>
       <c r="P16" s="7" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Q16" s="7" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="R16" s="7" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="S16" s="7" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -1908,10 +1327,10 @@
         <v>17</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D17" s="5"/>
       <c r="E17" s="6"/>
@@ -1925,19 +1344,19 @@
       <c r="M17" s="7"/>
       <c r="N17" s="7"/>
       <c r="O17" s="7" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="P17" s="7" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Q17" s="7" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="R17" s="7" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="S17" s="7" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -1945,10 +1364,10 @@
         <v>18</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D18" s="5"/>
       <c r="E18" s="6"/>
@@ -1960,10 +1379,10 @@
       <c r="K18" s="7"/>
       <c r="L18" s="7"/>
       <c r="M18" s="7" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="N18" s="7" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="O18" s="7"/>
       <c r="P18" s="7"/>
@@ -1976,10 +1395,10 @@
         <v>19</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="6"/>
@@ -2005,10 +1424,10 @@
         <v>20</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D20" s="5"/>
       <c r="E20" s="6"/>
@@ -2034,10 +1453,10 @@
         <v>21</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="6"/>
@@ -2063,10 +1482,10 @@
         <v>22</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D22" s="5"/>
       <c r="E22" s="6"/>
@@ -2092,10 +1511,10 @@
         <v>23</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D23" s="5"/>
       <c r="E23" s="6"/>
@@ -2121,10 +1540,10 @@
         <v>24</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D24" s="5"/>
       <c r="E24" s="6"/>
@@ -2150,10 +1569,10 @@
         <v>25</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D25" s="5"/>
       <c r="E25" s="6"/>
@@ -2179,10 +1598,10 @@
         <v>26</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="6"/>
@@ -2194,25 +1613,25 @@
       <c r="K26" s="7"/>
       <c r="L26" s="7"/>
       <c r="M26" s="7" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="N26" s="7" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="O26" s="7" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="P26" s="7" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="Q26" s="7" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="R26" s="7" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="S26" s="7" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27" spans="1:19">
@@ -2220,10 +1639,10 @@
         <v>27</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="D27" s="5"/>
       <c r="E27" s="6"/>
@@ -2237,19 +1656,19 @@
       <c r="M27" s="7"/>
       <c r="N27" s="7"/>
       <c r="O27" s="7" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="P27" s="7" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="Q27" s="7" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="R27" s="7" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="S27" s="7" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28" spans="1:19">
@@ -2257,10 +1676,10 @@
         <v>28</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="D28" s="5"/>
       <c r="E28" s="6"/>
@@ -2274,19 +1693,19 @@
       <c r="M28" s="7"/>
       <c r="N28" s="7"/>
       <c r="O28" s="7" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="P28" s="7" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="Q28" s="7" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="R28" s="7" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="S28" s="7" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29" spans="1:19">
@@ -2294,10 +1713,10 @@
         <v>29</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="D29" s="5"/>
       <c r="E29" s="6"/>
@@ -2311,19 +1730,19 @@
       <c r="M29" s="7"/>
       <c r="N29" s="7"/>
       <c r="O29" s="7" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="P29" s="7" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="Q29" s="7" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="R29" s="7" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="S29" s="7" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
     <row r="30" spans="1:19">
@@ -2331,10 +1750,10 @@
         <v>30</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="D30" s="5"/>
       <c r="E30" s="6"/>
@@ -2346,13 +1765,13 @@
       <c r="K30" s="7"/>
       <c r="L30" s="7"/>
       <c r="M30" s="7" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="N30" s="7" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="O30" s="7" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="P30" s="7"/>
       <c r="Q30" s="7"/>
@@ -2364,10 +1783,10 @@
         <v>31</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="D31" s="5"/>
       <c r="E31" s="6"/>
@@ -2379,19 +1798,19 @@
       <c r="K31" s="7"/>
       <c r="L31" s="7"/>
       <c r="M31" s="7" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="N31" s="7" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="O31" s="7" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="P31" s="7" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Q31" s="7" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="R31" s="7"/>
       <c r="S31" s="7"/>
@@ -2401,10 +1820,10 @@
         <v>32</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="D32" s="5"/>
       <c r="E32" s="6"/>
@@ -2416,19 +1835,19 @@
       <c r="K32" s="7"/>
       <c r="L32" s="7"/>
       <c r="M32" s="7" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="N32" s="7" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="O32" s="7" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="P32" s="7" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Q32" s="7" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="R32" s="7"/>
       <c r="S32" s="7"/>
@@ -2438,56 +1857,56 @@
         <v>33</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="D33" s="5"/>
       <c r="E33" s="6" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="F33" s="6">
         <v>1</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="H33" s="7" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="I33" s="7" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="J33" s="7" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="K33" s="7" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="L33" s="7" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="M33" s="7" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="N33" s="7" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="O33" s="7" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="P33" s="7" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="Q33" s="7" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="R33" s="7" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="S33" s="7" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
     <row r="34" spans="1:19">
@@ -2495,10 +1914,10 @@
         <v>34</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="D34" s="8"/>
       <c r="E34" s="9"/>
@@ -2515,10 +1934,10 @@
       <c r="P34" s="10"/>
       <c r="Q34" s="7"/>
       <c r="R34" s="7" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="S34" s="7" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="35" spans="1:19">
@@ -2526,56 +1945,56 @@
         <v>35</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="D35" s="8"/>
       <c r="E35" s="9" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="F35" s="9">
         <v>1</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="J35" s="10" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="K35" s="10" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="L35" s="10" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="M35" s="10" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Q35" s="7" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="R35" s="7" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="S35" s="7" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="36" spans="1:19">
@@ -2583,10 +2002,10 @@
         <v>36</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="D36" s="8"/>
       <c r="E36" s="9" t="s">
@@ -2612,10 +2031,10 @@
         <v>37</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="D37" s="8"/>
       <c r="E37" s="9" t="s">
@@ -2641,10 +2060,10 @@
         <v>38</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="D38" s="8"/>
       <c r="E38" s="9" t="s">
@@ -2670,14 +2089,14 @@
         <v>39</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D39" s="8"/>
       <c r="E39" s="9" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="F39" s="9"/>
       <c r="G39" s="10"/>
@@ -2699,14 +2118,14 @@
         <v>40</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="D40" s="8"/>
       <c r="E40" s="9" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="F40" s="9"/>
       <c r="G40" s="10"/>
@@ -2728,14 +2147,14 @@
         <v>41</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="D41" s="8"/>
       <c r="E41" s="9" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="F41" s="9"/>
       <c r="G41" s="10"/>
@@ -2757,14 +2176,14 @@
         <v>42</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="D42" s="8"/>
       <c r="E42" s="9" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="F42" s="9"/>
       <c r="G42" s="10"/>
@@ -2786,14 +2205,14 @@
         <v>43</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="D43" s="8"/>
       <c r="E43" s="9" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="F43" s="9"/>
       <c r="G43" s="10"/>
@@ -2815,10 +2234,10 @@
         <v>44</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="D44" s="8"/>
       <c r="E44" s="9"/>
@@ -2844,10 +2263,10 @@
         <v>45</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="D45" s="8"/>
       <c r="E45" s="9"/>
@@ -2873,10 +2292,10 @@
         <v>46</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="D46" s="8"/>
       <c r="E46" s="9"/>
@@ -2902,15 +2321,15 @@
         <v>47</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D47" s="8"/>
       <c r="E47" s="9"/>
       <c r="F47" s="9" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="G47" s="10"/>
       <c r="H47" s="10"/>
@@ -2931,15 +2350,15 @@
         <v>48</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="D48" s="8"/>
       <c r="E48" s="9"/>
       <c r="F48" s="9" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="G48" s="10"/>
       <c r="H48" s="10"/>
@@ -2960,15 +2379,15 @@
         <v>49</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="D49" s="8"/>
       <c r="E49" s="9"/>
       <c r="F49" s="9" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="G49" s="10"/>
       <c r="H49" s="10"/>
@@ -2989,15 +2408,15 @@
         <v>50</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="D50" s="8"/>
       <c r="E50" s="9"/>
       <c r="F50" s="9" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="G50" s="10"/>
       <c r="H50" s="10"/>
@@ -3018,15 +2437,15 @@
         <v>51</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="D51" s="8"/>
       <c r="E51" s="9"/>
       <c r="F51" s="9" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="G51" s="10"/>
       <c r="H51" s="10"/>
@@ -3047,10 +2466,10 @@
         <v>52</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="D52" s="8"/>
       <c r="E52" s="9"/>
@@ -3076,10 +2495,10 @@
         <v>53</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="D53" s="8"/>
       <c r="E53" s="9"/>
@@ -3105,10 +2524,10 @@
         <v>54</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="D54" s="8"/>
       <c r="E54" s="9"/>
@@ -3134,10 +2553,10 @@
         <v>55</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D55" s="8"/>
       <c r="E55" s="9"/>
@@ -3163,16 +2582,16 @@
         <v>56</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D56" s="8"/>
       <c r="E56" s="9"/>
       <c r="F56" s="9"/>
       <c r="G56" s="10" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="H56" s="10"/>
       <c r="I56" s="10"/>
@@ -3192,16 +2611,16 @@
         <v>57</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="D57" s="8"/>
       <c r="E57" s="9"/>
       <c r="F57" s="9"/>
       <c r="G57" s="10" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="H57" s="10"/>
       <c r="I57" s="10"/>
@@ -3221,16 +2640,16 @@
         <v>58</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="D58" s="8"/>
       <c r="E58" s="9"/>
       <c r="F58" s="9"/>
       <c r="G58" s="10" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="H58" s="10"/>
       <c r="I58" s="10"/>
@@ -3250,16 +2669,16 @@
         <v>59</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="D59" s="8"/>
       <c r="E59" s="9"/>
       <c r="F59" s="9"/>
       <c r="G59" s="10" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="H59" s="10"/>
       <c r="I59" s="10"/>
@@ -3279,16 +2698,16 @@
         <v>60</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="D60" s="8"/>
       <c r="E60" s="9"/>
       <c r="F60" s="9"/>
       <c r="G60" s="10" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H60" s="10"/>
       <c r="I60" s="10"/>
@@ -3308,16 +2727,16 @@
         <v>61</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="D61" s="8"/>
       <c r="E61" s="9"/>
       <c r="F61" s="9"/>
       <c r="G61" s="10" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H61" s="10"/>
       <c r="I61" s="10"/>
@@ -3337,10 +2756,10 @@
         <v>62</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="D62" s="8"/>
       <c r="E62" s="9"/>
@@ -3366,10 +2785,10 @@
         <v>63</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="D63" s="8"/>
       <c r="E63" s="9"/>
@@ -3395,10 +2814,10 @@
         <v>64</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="D64" s="8"/>
       <c r="E64" s="9"/>
@@ -3424,17 +2843,17 @@
         <v>65</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D65" s="8"/>
       <c r="E65" s="9"/>
       <c r="F65" s="9"/>
       <c r="G65" s="10"/>
       <c r="H65" s="10" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="I65" s="10"/>
       <c r="J65" s="10"/>
@@ -3453,17 +2872,17 @@
         <v>66</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="D66" s="8"/>
       <c r="E66" s="9"/>
       <c r="F66" s="9"/>
       <c r="G66" s="10"/>
       <c r="H66" s="10" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="I66" s="10"/>
       <c r="J66" s="10"/>
@@ -3482,17 +2901,17 @@
         <v>67</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="D67" s="8"/>
       <c r="E67" s="9"/>
       <c r="F67" s="9"/>
       <c r="G67" s="10"/>
       <c r="H67" s="10" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="I67" s="10"/>
       <c r="J67" s="10"/>
@@ -3511,17 +2930,17 @@
         <v>68</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="D68" s="5"/>
       <c r="E68" s="6"/>
       <c r="F68" s="9"/>
       <c r="G68" s="10"/>
       <c r="H68" s="10" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="I68" s="10"/>
       <c r="J68" s="10"/>
@@ -3540,17 +2959,17 @@
         <v>69</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="D69" s="5"/>
       <c r="E69" s="6"/>
       <c r="F69" s="9"/>
       <c r="G69" s="10"/>
       <c r="H69" s="10" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="I69" s="10"/>
       <c r="J69" s="10"/>
@@ -3569,17 +2988,17 @@
         <v>70</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="D70" s="5"/>
       <c r="E70" s="6"/>
       <c r="F70" s="9"/>
       <c r="G70" s="10"/>
       <c r="H70" s="10" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="I70" s="10"/>
       <c r="J70" s="10"/>
@@ -3598,7 +3017,7 @@
         <v>71</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="C71" s="5" t="s">
         <v>9</v>
@@ -3627,10 +3046,10 @@
         <v>72</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="D72" s="5"/>
       <c r="E72" s="11"/>
@@ -3656,10 +3075,10 @@
         <v>73</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D73" s="5"/>
       <c r="E73" s="11"/>
@@ -3685,10 +3104,10 @@
         <v>74</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D74" s="5"/>
       <c r="E74" s="11"/>
@@ -3714,10 +3133,10 @@
         <v>75</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="D75" s="5"/>
       <c r="E75" s="11"/>
@@ -3743,10 +3162,10 @@
         <v>76</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="D76" s="5"/>
       <c r="E76" s="11"/>
@@ -3772,10 +3191,10 @@
         <v>77</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="D77" s="5"/>
       <c r="E77" s="11"/>
@@ -3801,10 +3220,10 @@
         <v>78</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="D78" s="5"/>
       <c r="E78" s="11"/>
@@ -3812,7 +3231,7 @@
       <c r="G78" s="3"/>
       <c r="H78" s="3"/>
       <c r="I78" s="3" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="J78" s="3"/>
       <c r="K78" s="3"/>
@@ -3830,10 +3249,10 @@
         <v>79</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="D79" s="5"/>
       <c r="E79" s="11"/>
@@ -3841,7 +3260,7 @@
       <c r="G79" s="3"/>
       <c r="H79" s="3"/>
       <c r="I79" s="3" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="J79" s="3"/>
       <c r="K79" s="3"/>
@@ -3859,7 +3278,7 @@
         <v>80</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="C80" s="5" t="s">
         <v>9</v>
@@ -3888,10 +3307,10 @@
         <v>81</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="D81" s="5"/>
       <c r="E81" s="11"/>
@@ -3917,10 +3336,10 @@
         <v>82</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D82" s="5"/>
       <c r="E82" s="11"/>
@@ -3946,10 +3365,10 @@
         <v>83</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D83" s="5"/>
       <c r="E83" s="11"/>
@@ -3975,10 +3394,10 @@
         <v>84</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="D84" s="5"/>
       <c r="E84" s="11"/>
@@ -4004,10 +3423,10 @@
         <v>85</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="D85" s="5"/>
       <c r="E85" s="11"/>
@@ -4033,10 +3452,10 @@
         <v>86</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="D86" s="5"/>
       <c r="E86" s="11"/>
@@ -4062,10 +3481,10 @@
         <v>87</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="D87" s="5"/>
       <c r="E87" s="11"/>
@@ -4074,7 +3493,7 @@
       <c r="H87" s="3"/>
       <c r="I87" s="3"/>
       <c r="J87" s="3" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="K87" s="3"/>
       <c r="L87" s="3"/>
@@ -4091,10 +3510,10 @@
         <v>88</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="D88" s="5"/>
       <c r="E88" s="11"/>
@@ -4103,7 +3522,7 @@
       <c r="H88" s="3"/>
       <c r="I88" s="3"/>
       <c r="J88" s="3" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="K88" s="3"/>
       <c r="L88" s="3"/>
@@ -4120,10 +3539,10 @@
         <v>89</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="D89" s="5"/>
       <c r="E89" s="11"/>
@@ -4149,10 +3568,10 @@
         <v>90</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="D90" s="5"/>
       <c r="E90" s="11"/>
@@ -4178,10 +3597,10 @@
         <v>91</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="D91" s="5"/>
       <c r="E91" s="11"/>
@@ -4207,10 +3626,10 @@
         <v>92</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D92" s="5"/>
       <c r="E92" s="11"/>
@@ -4220,7 +3639,7 @@
       <c r="I92" s="3"/>
       <c r="J92" s="3"/>
       <c r="K92" s="10" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="L92" s="3"/>
       <c r="M92" s="3"/>
@@ -4236,10 +3655,10 @@
         <v>93</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="D93" s="5"/>
       <c r="E93" s="11"/>
@@ -4249,7 +3668,7 @@
       <c r="I93" s="3"/>
       <c r="J93" s="3"/>
       <c r="K93" s="10" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="L93" s="3"/>
       <c r="M93" s="3"/>
@@ -4265,10 +3684,10 @@
         <v>94</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="D94" s="5"/>
       <c r="E94" s="11"/>
@@ -4278,7 +3697,7 @@
       <c r="I94" s="3"/>
       <c r="J94" s="3"/>
       <c r="K94" s="10" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="L94" s="3"/>
       <c r="M94" s="3"/>
@@ -4294,10 +3713,10 @@
         <v>95</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="D95" s="5"/>
       <c r="E95" s="11"/>
@@ -4307,7 +3726,7 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="10" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
@@ -4323,10 +3742,10 @@
         <v>96</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="D96" s="5"/>
       <c r="E96" s="11"/>
@@ -4336,7 +3755,7 @@
       <c r="I96" s="3"/>
       <c r="J96" s="3"/>
       <c r="K96" s="10" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="L96" s="3"/>
       <c r="M96" s="3"/>
@@ -4352,10 +3771,10 @@
         <v>97</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="D97" s="5"/>
       <c r="E97" s="11"/>
@@ -4365,7 +3784,7 @@
       <c r="I97" s="3"/>
       <c r="J97" s="3"/>
       <c r="K97" s="10" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="L97" s="3"/>
       <c r="M97" s="3"/>
@@ -4381,7 +3800,7 @@
         <v>98</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="C98" s="5" t="s">
         <v>9</v>
@@ -4410,10 +3829,10 @@
         <v>99</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="D99" s="5"/>
       <c r="E99" s="11"/>
@@ -4439,10 +3858,10 @@
         <v>100</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D100" s="5"/>
       <c r="E100" s="11"/>
@@ -4468,10 +3887,10 @@
         <v>101</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D101" s="5"/>
       <c r="E101" s="11"/>
@@ -4497,10 +3916,10 @@
         <v>102</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="D102" s="5"/>
       <c r="E102" s="11"/>
@@ -4526,10 +3945,10 @@
         <v>103</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="D103" s="5"/>
       <c r="E103" s="11"/>
@@ -4555,10 +3974,10 @@
         <v>104</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="D104" s="5"/>
       <c r="E104" s="11"/>
@@ -4584,10 +4003,10 @@
         <v>105</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="D105" s="8"/>
       <c r="E105" s="9"/>
@@ -4598,7 +4017,7 @@
       <c r="J105" s="3"/>
       <c r="K105" s="3"/>
       <c r="L105" s="3" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="M105" s="3"/>
       <c r="N105" s="3"/>
@@ -4613,10 +4032,10 @@
         <v>106</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="D106" s="8"/>
       <c r="E106" s="9"/>
@@ -4627,7 +4046,7 @@
       <c r="J106" s="3"/>
       <c r="K106" s="3"/>
       <c r="L106" s="3" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="M106" s="3"/>
       <c r="N106" s="3"/>
@@ -4642,10 +4061,10 @@
         <v>107</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="D107" s="8"/>
       <c r="E107" s="9">
@@ -4671,10 +4090,10 @@
         <v>108</v>
       </c>
       <c r="B108" s="12" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="C108" s="12" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="D108" s="3"/>
       <c r="E108" s="9"/>
@@ -4700,10 +4119,10 @@
         <v>109</v>
       </c>
       <c r="B109" s="12" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="C109" s="12" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="D109" s="3"/>
       <c r="E109" s="9"/>
@@ -4729,10 +4148,10 @@
         <v>110</v>
       </c>
       <c r="B110" s="12" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="C110" s="12" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="D110" s="3"/>
       <c r="E110" s="9"/>
@@ -4746,7 +4165,7 @@
       <c r="M110" s="3"/>
       <c r="N110" s="3"/>
       <c r="O110" s="3" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="P110" s="3"/>
       <c r="Q110" s="3"/>
@@ -4758,10 +4177,10 @@
         <v>111</v>
       </c>
       <c r="B111" s="12" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="C111" s="12" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="D111" s="3"/>
       <c r="E111" s="9"/>
@@ -4776,7 +4195,7 @@
       <c r="N111" s="3"/>
       <c r="O111" s="3"/>
       <c r="P111" s="3" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Q111" s="3"/>
       <c r="R111" s="3"/>
@@ -4787,10 +4206,10 @@
         <v>112</v>
       </c>
       <c r="B112" s="12" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="C112" s="12" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="D112" s="12"/>
       <c r="E112" s="11"/>
@@ -4806,7 +4225,7 @@
       <c r="O112" s="3"/>
       <c r="P112" s="3"/>
       <c r="Q112" s="3" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="R112" s="3"/>
       <c r="S112" s="3"/>
@@ -4816,10 +4235,10 @@
         <v>113</v>
       </c>
       <c r="B113" s="12" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="C113" s="12" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="D113" s="12"/>
       <c r="E113" s="11"/>
@@ -4836,7 +4255,7 @@
       <c r="P113" s="3"/>
       <c r="Q113" s="3"/>
       <c r="R113" s="3" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="S113" s="3"/>
     </row>
@@ -4845,10 +4264,10 @@
         <v>114</v>
       </c>
       <c r="B114" s="12" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="C114" s="12" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="D114" s="12"/>
       <c r="E114" s="11"/>
@@ -4866,12 +4285,11 @@
       <c r="Q114" s="3"/>
       <c r="R114" s="3"/>
       <c r="S114" s="3" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>